--- a/template.xlsx
+++ b/template.xlsx
@@ -8,19 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kotel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34546283-85F4-46B5-9FB5-C1A17C030351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B5F0E5-494C-422A-8E61-6292B7793832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FRD kiszedés" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
   <si>
     <t>Hét #</t>
   </si>
@@ -38,6 +50,21 @@
   </si>
   <si>
     <t>VISSZA</t>
+  </si>
+  <si>
+    <t>Hétfő</t>
+  </si>
+  <si>
+    <t>Kedd</t>
+  </si>
+  <si>
+    <t>Szerda</t>
+  </si>
+  <si>
+    <t>Csütörtök</t>
+  </si>
+  <si>
+    <t>Péntek</t>
   </si>
 </sst>
 </file>
@@ -903,19 +930,29 @@
       <c r="P1" s="33"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34"/>
+      <c r="A2" s="34" t="s">
+        <v>6</v>
+      </c>
       <c r="B2" s="35"/>
       <c r="C2" s="36"/>
-      <c r="D2" s="34"/>
+      <c r="D2" s="34" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="35"/>
       <c r="F2" s="36"/>
-      <c r="G2" s="34"/>
+      <c r="G2" s="34" t="s">
+        <v>8</v>
+      </c>
       <c r="H2" s="35"/>
       <c r="I2" s="36"/>
-      <c r="J2" s="34"/>
+      <c r="J2" s="34" t="s">
+        <v>9</v>
+      </c>
       <c r="K2" s="35"/>
       <c r="L2" s="36"/>
-      <c r="M2" s="23"/>
+      <c r="M2" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="N2" s="24"/>
       <c r="O2" s="25"/>
       <c r="P2" s="1"/>
@@ -1514,29 +1551,35 @@
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="15">
+        <f>SUM(C4:C33)</f>
         <v>0</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="F34" s="15">
+        <f>SUM(F4:F33)</f>
         <v>0</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="14"/>
       <c r="I34" s="15">
+        <f>SUM(I4:I33)</f>
         <v>0</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="14"/>
       <c r="L34" s="15">
+        <f>SUM(L4:L33)</f>
         <v>0</v>
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="14"/>
       <c r="O34" s="15">
+        <f>SUM(O4:O33)</f>
         <v>0</v>
       </c>
       <c r="P34" s="16">
+        <f>SUM(C34,F34,I34,L34,O34)</f>
         <v>0</v>
       </c>
     </row>
@@ -1620,29 +1663,35 @@
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="17">
+        <f>SUM(C36:C38)</f>
         <v>0</v>
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="19"/>
       <c r="F39" s="17">
+        <f>SUM(F36:F38)</f>
         <v>0</v>
       </c>
       <c r="G39" s="18"/>
       <c r="H39" s="19"/>
       <c r="I39" s="17">
+        <f>SUM(I36:I38)</f>
         <v>0</v>
       </c>
       <c r="J39" s="18"/>
       <c r="K39" s="19"/>
       <c r="L39" s="17">
+        <f>SUM(L36:L38)</f>
         <v>0</v>
       </c>
       <c r="M39" s="18"/>
       <c r="N39" s="19"/>
       <c r="O39" s="17">
+        <f>SUM(O36:O38)</f>
         <v>0</v>
       </c>
       <c r="P39" s="20">
+        <f>SUM(O39,L39,I39,F39,C39)</f>
         <v>0</v>
       </c>
     </row>
